--- a/public/Excel_template/입고.xlsx
+++ b/public/Excel_template/입고.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ABC_product\product_manage\public\Excel_template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78A7E3C-B729-40DB-87D4-0F7ADF819586}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4102509F-68E1-4FF8-B987-1D334A5AC546}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28770" windowHeight="12135" tabRatio="610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,7 @@
     <sheet name="입고" sheetId="117" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">입고!$A$6:$O$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">입고!$A$1:$P$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">입고!$A$6:$O$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">입고!$5:$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -119,7 +118,7 @@
     <numFmt numFmtId="176" formatCode="#,##0_);[Red]\(#,##0\)"/>
     <numFmt numFmtId="177" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,13 +217,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="KoPubWorld돋움체 Light"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <b/>
       <sz val="24"/>
       <color rgb="FF000000"/>
@@ -236,14 +228,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="KoPubWorld돋움체_Pro Bold"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF008000"/>
-      <name val="KoPubWorld돋움체 Light"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -262,7 +246,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -315,43 +299,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -418,79 +365,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="hair">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="hair">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="hair">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="hair">
-        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1132,7 +1006,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1148,7 +1022,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1172,44 +1046,14 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="13" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="16" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1223,163 +1067,133 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="8" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="32" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="28" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="28" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="32" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="30" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="31" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="28" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="39" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="40" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="12" fillId="0" borderId="18" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="35" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="36" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1859,16 +1673,16 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S80"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.95" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.875" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="5.625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="6.875" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.625" style="19" customWidth="1"/>
     <col min="7" max="7" width="18.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35" style="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="26" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="35" style="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="16" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.625" style="4" customWidth="1"/>
     <col min="11" max="11" width="8.625" style="4" customWidth="1"/>
     <col min="12" max="12" width="15.125" style="4" customWidth="1"/>
@@ -1889,41 +1703,41 @@
       <c r="Q1" s="2"/>
     </row>
     <row r="2" spans="1:19" ht="24.95" customHeight="1">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="56" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="74"/>
-      <c r="J2" s="74"/>
-      <c r="K2" s="74"/>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:19" ht="24.95" customHeight="1">
-      <c r="A3" s="74"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="74"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="74"/>
-      <c r="J3" s="74"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
-      <c r="M3" s="74"/>
-      <c r="N3" s="74"/>
-      <c r="O3" s="74"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:19" ht="20.100000000000001" customHeight="1">
@@ -1943,48 +1757,48 @@
       </c>
     </row>
     <row r="5" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A5" s="75" t="s">
+      <c r="A5" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="70" t="s">
+      <c r="C5" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="72" t="s">
+      <c r="D5" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="E5" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="70" t="s">
+      <c r="F5" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="72" t="s">
+      <c r="G5" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="77" t="s">
+      <c r="H5" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="70" t="s">
+      <c r="I5" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="72" t="s">
+      <c r="J5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="70" t="s">
+      <c r="K5" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="81" t="s">
+      <c r="L5" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="M5" s="82"/>
-      <c r="N5" s="79" t="s">
+      <c r="M5" s="62"/>
+      <c r="N5" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="80"/>
-      <c r="P5" s="75" t="s">
+      <c r="O5" s="60"/>
+      <c r="P5" s="50" t="s">
         <v>19</v>
       </c>
       <c r="Q5" s="11"/>
@@ -1992,21 +1806,21 @@
       <c r="S5" s="10"/>
     </row>
     <row r="6" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A6" s="76"/>
-      <c r="B6" s="73"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="73"/>
-      <c r="E6" s="78"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="78"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="62" t="s">
+      <c r="A6" s="51"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="M6" s="57" t="s">
+      <c r="M6" s="41" t="s">
         <v>14</v>
       </c>
       <c r="N6" s="13" t="s">
@@ -2015,1245 +1829,1096 @@
       <c r="O6" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="P6" s="76"/>
+      <c r="P6" s="51"/>
       <c r="Q6" s="11"/>
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
     </row>
     <row r="7" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
       <c r="A7" s="15"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="35"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="59"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="49"/>
-      <c r="O7" s="44"/>
-      <c r="P7" s="66"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="43"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="30"/>
+      <c r="P7" s="49"/>
       <c r="Q7" s="11"/>
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
     </row>
     <row r="8" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A8" s="33"/>
-      <c r="B8" s="37"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="63"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="64"/>
-      <c r="O8" s="65"/>
-      <c r="P8" s="66"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="44"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="47"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="49"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="10"/>
       <c r="S8" s="10"/>
     </row>
     <row r="9" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A9" s="33"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="63"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="64"/>
-      <c r="O9" s="65"/>
-      <c r="P9" s="66"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="49"/>
       <c r="Q9" s="11"/>
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
     </row>
     <row r="10" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A10" s="33"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="41"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="51"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="66"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="37"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="49"/>
       <c r="Q10" s="11"/>
       <c r="R10" s="10"/>
       <c r="S10" s="10"/>
     </row>
     <row r="11" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="37"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="45"/>
-      <c r="P11" s="66"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="49"/>
       <c r="Q11" s="11"/>
       <c r="R11" s="10"/>
       <c r="S11" s="10"/>
     </row>
     <row r="12" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A12" s="33"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="41"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="46"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="66"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="49"/>
       <c r="Q12" s="11"/>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
     </row>
     <row r="13" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="37"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="41"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="66"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="49"/>
       <c r="Q13" s="11"/>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
     </row>
     <row r="14" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A14" s="33"/>
-      <c r="B14" s="37"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="60"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="46"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="66"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="44"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="49"/>
       <c r="Q14" s="11"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
     </row>
     <row r="15" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="37"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="60"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="52"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="66"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="44"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="49"/>
       <c r="Q15" s="11"/>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
     </row>
     <row r="16" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A16" s="33"/>
-      <c r="B16" s="37"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="53"/>
-      <c r="O16" s="48"/>
-      <c r="P16" s="66"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="49"/>
       <c r="Q16" s="11"/>
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
     </row>
-    <row r="17" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="60"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-    </row>
-    <row r="18" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A18" s="33"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="60"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="54"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="11"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-    </row>
-    <row r="19" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A19" s="33"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="54"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-    </row>
-    <row r="20" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A20" s="33"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="60"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-    </row>
-    <row r="21" spans="1:19" s="12" customFormat="1" ht="30" customHeight="1">
-      <c r="A21" s="33"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="41"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="38"/>
-      <c r="L21" s="61"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="30"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="66"/>
-      <c r="Q21" s="11"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-    </row>
-    <row r="22" spans="1:19" ht="35.1" customHeight="1">
-      <c r="A22" s="67"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="69"/>
-      <c r="L22" s="56"/>
+    <row r="17" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="Q17" s="2"/>
+    </row>
+    <row r="18" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="Q18" s="2"/>
+    </row>
+    <row r="19" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="Q19" s="2"/>
+    </row>
+    <row r="20" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="Q20" s="2"/>
+    </row>
+    <row r="21" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="Q21" s="2"/>
+    </row>
+    <row r="22" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
       <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="1:19" s="8" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="1"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="Q22" s="2"/>
+    </row>
+    <row r="23" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
       <c r="Q23" s="2"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-    </row>
-    <row r="24" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
+    </row>
+    <row r="24" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="26"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
       <c r="Q24" s="2"/>
     </row>
-    <row r="25" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C25" s="29"/>
-      <c r="D25" s="29"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
+    <row r="25" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
       <c r="Q25" s="2"/>
     </row>
-    <row r="26" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
+    <row r="26" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
       <c r="N26" s="8"/>
       <c r="O26" s="8"/>
       <c r="Q26" s="2"/>
     </row>
-    <row r="27" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
+    <row r="27" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
       <c r="N27" s="8"/>
       <c r="O27" s="8"/>
       <c r="Q27" s="2"/>
     </row>
-    <row r="28" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
+    <row r="28" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="4"/>
-      <c r="H28" s="26"/>
-      <c r="I28" s="26"/>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
       <c r="N28" s="8"/>
       <c r="O28" s="8"/>
       <c r="Q28" s="2"/>
     </row>
-    <row r="29" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
+    <row r="29" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="4"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
       <c r="Q29" s="2"/>
     </row>
-    <row r="30" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
+    <row r="30" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
       <c r="G30" s="4"/>
-      <c r="H30" s="26"/>
-      <c r="I30" s="26"/>
-      <c r="J30" s="26"/>
-      <c r="K30" s="26"/>
-      <c r="L30" s="26"/>
-      <c r="M30" s="26"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
       <c r="Q30" s="2"/>
     </row>
-    <row r="31" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
+    <row r="31" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
       <c r="G31" s="4"/>
-      <c r="H31" s="26"/>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="26"/>
-      <c r="L31" s="26"/>
-      <c r="M31" s="26"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
       <c r="Q31" s="2"/>
     </row>
-    <row r="32" spans="1:19" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
+    <row r="32" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
       <c r="G32" s="4"/>
-      <c r="H32" s="26"/>
-      <c r="I32" s="26"/>
-      <c r="J32" s="26"/>
-      <c r="K32" s="26"/>
-      <c r="L32" s="26"/>
-      <c r="M32" s="26"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
       <c r="Q32" s="2"/>
     </row>
     <row r="33" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
       <c r="G33" s="4"/>
-      <c r="H33" s="26"/>
-      <c r="I33" s="26"/>
-      <c r="J33" s="26"/>
-      <c r="K33" s="26"/>
-      <c r="L33" s="26"/>
-      <c r="M33" s="26"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
       <c r="N33" s="8"/>
       <c r="O33" s="8"/>
       <c r="Q33" s="2"/>
     </row>
     <row r="34" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
       <c r="G34" s="4"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
       <c r="N34" s="8"/>
       <c r="O34" s="8"/>
       <c r="Q34" s="2"/>
     </row>
     <row r="35" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C35" s="29"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
       <c r="G35" s="4"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="26"/>
-      <c r="L35" s="26"/>
-      <c r="M35" s="26"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
       <c r="N35" s="8"/>
       <c r="O35" s="8"/>
       <c r="Q35" s="2"/>
     </row>
     <row r="36" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="4"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
       <c r="N36" s="8"/>
       <c r="O36" s="8"/>
       <c r="Q36" s="2"/>
     </row>
     <row r="37" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="4"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
       <c r="N37" s="8"/>
       <c r="O37" s="8"/>
       <c r="Q37" s="2"/>
     </row>
     <row r="38" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
       <c r="G38" s="4"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
       <c r="N38" s="8"/>
       <c r="O38" s="8"/>
       <c r="Q38" s="2"/>
     </row>
     <row r="39" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
       <c r="G39" s="4"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="26"/>
-      <c r="M39" s="26"/>
+      <c r="H39" s="16"/>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+      <c r="M39" s="16"/>
       <c r="N39" s="8"/>
       <c r="O39" s="8"/>
       <c r="Q39" s="2"/>
     </row>
     <row r="40" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
       <c r="G40" s="4"/>
-      <c r="H40" s="26"/>
-      <c r="I40" s="26"/>
-      <c r="J40" s="26"/>
-      <c r="K40" s="26"/>
-      <c r="L40" s="26"/>
-      <c r="M40" s="26"/>
+      <c r="H40" s="16"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
       <c r="N40" s="8"/>
       <c r="O40" s="8"/>
       <c r="Q40" s="2"/>
     </row>
     <row r="41" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
       <c r="G41" s="4"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="M41" s="26"/>
+      <c r="H41" s="16"/>
+      <c r="I41" s="16"/>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+      <c r="M41" s="16"/>
       <c r="N41" s="8"/>
       <c r="O41" s="8"/>
       <c r="Q41" s="2"/>
     </row>
     <row r="42" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
       <c r="G42" s="4"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="M42" s="26"/>
+      <c r="H42" s="16"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="16"/>
       <c r="N42" s="8"/>
       <c r="O42" s="8"/>
       <c r="Q42" s="2"/>
     </row>
     <row r="43" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
       <c r="G43" s="4"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
-      <c r="M43" s="26"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="16"/>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
       <c r="N43" s="8"/>
       <c r="O43" s="8"/>
       <c r="Q43" s="2"/>
     </row>
     <row r="44" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
       <c r="G44" s="4"/>
-      <c r="H44" s="26"/>
-      <c r="I44" s="26"/>
-      <c r="J44" s="26"/>
-      <c r="K44" s="26"/>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26"/>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16"/>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
       <c r="N44" s="8"/>
       <c r="O44" s="8"/>
       <c r="Q44" s="2"/>
     </row>
     <row r="45" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
       <c r="G45" s="4"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
       <c r="N45" s="8"/>
       <c r="O45" s="8"/>
       <c r="Q45" s="2"/>
     </row>
     <row r="46" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="19"/>
       <c r="G46" s="4"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="K46" s="26"/>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26"/>
+      <c r="H46" s="16"/>
+      <c r="I46" s="16"/>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+      <c r="M46" s="16"/>
       <c r="N46" s="8"/>
       <c r="O46" s="8"/>
       <c r="Q46" s="2"/>
     </row>
     <row r="47" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
       <c r="G47" s="4"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
+      <c r="H47" s="16"/>
+      <c r="I47" s="16"/>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+      <c r="M47" s="16"/>
       <c r="N47" s="8"/>
       <c r="O47" s="8"/>
       <c r="Q47" s="2"/>
     </row>
     <row r="48" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="19"/>
       <c r="G48" s="4"/>
-      <c r="H48" s="26"/>
-      <c r="I48" s="26"/>
-      <c r="J48" s="26"/>
-      <c r="K48" s="26"/>
-      <c r="L48" s="26"/>
-      <c r="M48" s="26"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="16"/>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+      <c r="M48" s="16"/>
       <c r="N48" s="8"/>
       <c r="O48" s="8"/>
       <c r="Q48" s="2"/>
     </row>
     <row r="49" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
       <c r="G49" s="4"/>
-      <c r="H49" s="26"/>
-      <c r="I49" s="26"/>
-      <c r="J49" s="26"/>
-      <c r="K49" s="26"/>
-      <c r="L49" s="26"/>
-      <c r="M49" s="26"/>
+      <c r="H49" s="16"/>
+      <c r="I49" s="16"/>
+      <c r="J49" s="16"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+      <c r="M49" s="16"/>
       <c r="N49" s="8"/>
       <c r="O49" s="8"/>
       <c r="Q49" s="2"/>
     </row>
     <row r="50" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
       <c r="G50" s="4"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="26"/>
-      <c r="J50" s="26"/>
-      <c r="K50" s="26"/>
-      <c r="L50" s="26"/>
-      <c r="M50" s="26"/>
+      <c r="H50" s="16"/>
+      <c r="I50" s="16"/>
+      <c r="J50" s="16"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+      <c r="M50" s="16"/>
       <c r="N50" s="8"/>
       <c r="O50" s="8"/>
       <c r="Q50" s="2"/>
     </row>
     <row r="51" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
       <c r="G51" s="4"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
+      <c r="H51" s="16"/>
+      <c r="I51" s="16"/>
+      <c r="J51" s="16"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
       <c r="N51" s="8"/>
       <c r="O51" s="8"/>
       <c r="Q51" s="2"/>
     </row>
     <row r="52" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
       <c r="G52" s="4"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="26"/>
-      <c r="J52" s="26"/>
-      <c r="K52" s="26"/>
-      <c r="L52" s="26"/>
-      <c r="M52" s="26"/>
+      <c r="H52" s="16"/>
+      <c r="I52" s="16"/>
+      <c r="J52" s="16"/>
+      <c r="K52" s="16"/>
+      <c r="L52" s="16"/>
+      <c r="M52" s="16"/>
       <c r="N52" s="8"/>
       <c r="O52" s="8"/>
       <c r="Q52" s="2"/>
     </row>
     <row r="53" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
       <c r="G53" s="4"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="26"/>
-      <c r="J53" s="26"/>
-      <c r="K53" s="26"/>
-      <c r="L53" s="26"/>
-      <c r="M53" s="26"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="16"/>
+      <c r="L53" s="16"/>
+      <c r="M53" s="16"/>
       <c r="N53" s="8"/>
       <c r="O53" s="8"/>
       <c r="Q53" s="2"/>
     </row>
     <row r="54" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
       <c r="G54" s="4"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="26"/>
-      <c r="J54" s="26"/>
-      <c r="K54" s="26"/>
-      <c r="L54" s="26"/>
-      <c r="M54" s="26"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
       <c r="N54" s="8"/>
       <c r="O54" s="8"/>
       <c r="Q54" s="2"/>
     </row>
     <row r="55" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
       <c r="G55" s="4"/>
-      <c r="H55" s="26"/>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55" s="26"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
       <c r="Q55" s="2"/>
     </row>
     <row r="56" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
-      <c r="F56" s="29"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
       <c r="G56" s="4"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
-      <c r="M56" s="26"/>
+      <c r="H56" s="16"/>
+      <c r="I56" s="16"/>
+      <c r="J56" s="16"/>
+      <c r="K56" s="16"/>
+      <c r="L56" s="16"/>
+      <c r="M56" s="16"/>
       <c r="N56" s="8"/>
       <c r="O56" s="8"/>
       <c r="Q56" s="2"/>
     </row>
     <row r="57" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
       <c r="G57" s="4"/>
-      <c r="H57" s="26"/>
-      <c r="I57" s="26"/>
-      <c r="J57" s="26"/>
-      <c r="K57" s="26"/>
-      <c r="L57" s="26"/>
-      <c r="M57" s="26"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="16"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="16"/>
+      <c r="M57" s="16"/>
       <c r="N57" s="8"/>
       <c r="O57" s="8"/>
       <c r="Q57" s="2"/>
     </row>
     <row r="58" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
       <c r="G58" s="4"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="26"/>
-      <c r="M58" s="26"/>
+      <c r="H58" s="16"/>
+      <c r="I58" s="16"/>
+      <c r="J58" s="16"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
       <c r="N58" s="8"/>
       <c r="O58" s="8"/>
       <c r="Q58" s="2"/>
     </row>
     <row r="59" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
-      <c r="F59" s="29"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
       <c r="G59" s="4"/>
-      <c r="H59" s="26"/>
-      <c r="I59" s="26"/>
-      <c r="J59" s="26"/>
-      <c r="K59" s="26"/>
-      <c r="L59" s="26"/>
-      <c r="M59" s="26"/>
+      <c r="H59" s="16"/>
+      <c r="I59" s="16"/>
+      <c r="J59" s="16"/>
+      <c r="K59" s="16"/>
+      <c r="L59" s="16"/>
+      <c r="M59" s="16"/>
       <c r="N59" s="8"/>
       <c r="O59" s="8"/>
       <c r="Q59" s="2"/>
     </row>
     <row r="60" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
       <c r="G60" s="4"/>
-      <c r="H60" s="26"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="26"/>
-      <c r="K60" s="26"/>
-      <c r="L60" s="26"/>
-      <c r="M60" s="26"/>
+      <c r="H60" s="16"/>
+      <c r="I60" s="16"/>
+      <c r="J60" s="16"/>
+      <c r="K60" s="16"/>
+      <c r="L60" s="16"/>
+      <c r="M60" s="16"/>
       <c r="N60" s="8"/>
       <c r="O60" s="8"/>
       <c r="Q60" s="2"/>
     </row>
     <row r="61" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
       <c r="G61" s="4"/>
-      <c r="H61" s="26"/>
-      <c r="I61" s="26"/>
-      <c r="J61" s="26"/>
-      <c r="K61" s="26"/>
-      <c r="L61" s="26"/>
-      <c r="M61" s="26"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
       <c r="N61" s="8"/>
       <c r="O61" s="8"/>
       <c r="Q61" s="2"/>
     </row>
     <row r="62" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
-      <c r="F62" s="29"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
       <c r="G62" s="4"/>
-      <c r="H62" s="26"/>
-      <c r="I62" s="26"/>
-      <c r="J62" s="26"/>
-      <c r="K62" s="26"/>
-      <c r="L62" s="26"/>
-      <c r="M62" s="26"/>
+      <c r="H62" s="16"/>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="16"/>
+      <c r="L62" s="16"/>
+      <c r="M62" s="16"/>
       <c r="N62" s="8"/>
       <c r="O62" s="8"/>
       <c r="Q62" s="2"/>
     </row>
     <row r="63" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="19"/>
+      <c r="F63" s="19"/>
       <c r="G63" s="4"/>
-      <c r="H63" s="26"/>
-      <c r="I63" s="26"/>
-      <c r="J63" s="26"/>
-      <c r="K63" s="26"/>
-      <c r="L63" s="26"/>
-      <c r="M63" s="26"/>
+      <c r="H63" s="16"/>
+      <c r="I63" s="16"/>
+      <c r="J63" s="16"/>
+      <c r="K63" s="16"/>
+      <c r="L63" s="16"/>
+      <c r="M63" s="16"/>
       <c r="N63" s="8"/>
       <c r="O63" s="8"/>
       <c r="Q63" s="2"/>
     </row>
     <row r="64" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
       <c r="G64" s="4"/>
-      <c r="H64" s="26"/>
-      <c r="I64" s="26"/>
-      <c r="J64" s="26"/>
-      <c r="K64" s="26"/>
-      <c r="L64" s="26"/>
-      <c r="M64" s="26"/>
+      <c r="H64" s="16"/>
+      <c r="I64" s="16"/>
+      <c r="J64" s="16"/>
+      <c r="K64" s="16"/>
+      <c r="L64" s="16"/>
+      <c r="M64" s="16"/>
       <c r="N64" s="8"/>
       <c r="O64" s="8"/>
       <c r="Q64" s="2"/>
     </row>
     <row r="65" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="19"/>
+      <c r="E65" s="19"/>
+      <c r="F65" s="19"/>
       <c r="G65" s="4"/>
-      <c r="H65" s="26"/>
-      <c r="I65" s="26"/>
-      <c r="J65" s="26"/>
-      <c r="K65" s="26"/>
-      <c r="L65" s="26"/>
-      <c r="M65" s="26"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="16"/>
+      <c r="K65" s="16"/>
+      <c r="L65" s="16"/>
+      <c r="M65" s="16"/>
       <c r="N65" s="8"/>
       <c r="O65" s="8"/>
       <c r="Q65" s="2"/>
     </row>
     <row r="66" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="19"/>
+      <c r="F66" s="19"/>
       <c r="G66" s="4"/>
-      <c r="H66" s="26"/>
-      <c r="I66" s="26"/>
-      <c r="J66" s="26"/>
-      <c r="K66" s="26"/>
-      <c r="L66" s="26"/>
-      <c r="M66" s="26"/>
+      <c r="H66" s="16"/>
+      <c r="I66" s="16"/>
+      <c r="J66" s="16"/>
+      <c r="K66" s="16"/>
+      <c r="L66" s="16"/>
+      <c r="M66" s="16"/>
       <c r="N66" s="8"/>
       <c r="O66" s="8"/>
       <c r="Q66" s="2"/>
     </row>
     <row r="67" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="19"/>
+      <c r="F67" s="19"/>
       <c r="G67" s="4"/>
-      <c r="H67" s="26"/>
-      <c r="I67" s="26"/>
-      <c r="J67" s="26"/>
-      <c r="K67" s="26"/>
-      <c r="L67" s="26"/>
-      <c r="M67" s="26"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
       <c r="N67" s="8"/>
       <c r="O67" s="8"/>
       <c r="Q67" s="2"/>
     </row>
     <row r="68" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
       <c r="G68" s="4"/>
-      <c r="H68" s="26"/>
-      <c r="I68" s="26"/>
-      <c r="J68" s="26"/>
-      <c r="K68" s="26"/>
-      <c r="L68" s="26"/>
-      <c r="M68" s="26"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="16"/>
+      <c r="J68" s="16"/>
+      <c r="K68" s="16"/>
+      <c r="L68" s="16"/>
+      <c r="M68" s="16"/>
       <c r="N68" s="8"/>
       <c r="O68" s="8"/>
       <c r="Q68" s="2"/>
     </row>
     <row r="69" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
       <c r="G69" s="4"/>
-      <c r="H69" s="26"/>
-      <c r="I69" s="26"/>
-      <c r="J69" s="26"/>
-      <c r="K69" s="26"/>
-      <c r="L69" s="26"/>
-      <c r="M69" s="26"/>
+      <c r="H69" s="16"/>
+      <c r="I69" s="16"/>
+      <c r="J69" s="16"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
       <c r="N69" s="8"/>
       <c r="O69" s="8"/>
       <c r="Q69" s="2"/>
     </row>
-    <row r="70" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="26"/>
-      <c r="K70" s="26"/>
-      <c r="L70" s="26"/>
-      <c r="M70" s="26"/>
-      <c r="N70" s="8"/>
-      <c r="O70" s="8"/>
-      <c r="Q70" s="2"/>
-    </row>
-    <row r="71" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="26"/>
-      <c r="I71" s="26"/>
-      <c r="J71" s="26"/>
-      <c r="K71" s="26"/>
-      <c r="L71" s="26"/>
-      <c r="M71" s="26"/>
-      <c r="N71" s="8"/>
-      <c r="O71" s="8"/>
-      <c r="Q71" s="2"/>
-    </row>
-    <row r="72" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="26"/>
-      <c r="I72" s="26"/>
-      <c r="J72" s="26"/>
-      <c r="K72" s="26"/>
-      <c r="L72" s="26"/>
-      <c r="M72" s="26"/>
-      <c r="N72" s="8"/>
-      <c r="O72" s="8"/>
-      <c r="Q72" s="2"/>
-    </row>
-    <row r="73" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
-      <c r="F73" s="29"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="26"/>
-      <c r="I73" s="26"/>
-      <c r="J73" s="26"/>
-      <c r="K73" s="26"/>
-      <c r="L73" s="26"/>
-      <c r="M73" s="26"/>
-      <c r="N73" s="8"/>
-      <c r="O73" s="8"/>
-      <c r="Q73" s="2"/>
-    </row>
-    <row r="74" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
-      <c r="F74" s="29"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="26"/>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
-      <c r="L74" s="26"/>
-      <c r="M74" s="26"/>
-      <c r="N74" s="8"/>
-      <c r="O74" s="8"/>
-      <c r="Q74" s="2"/>
-    </row>
-    <row r="75" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
-      <c r="L75" s="26"/>
-      <c r="M75" s="26"/>
-      <c r="N75" s="8"/>
-      <c r="O75" s="8"/>
-      <c r="Q75" s="2"/>
-    </row>
-    <row r="76" spans="3:17" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="26"/>
-      <c r="M76" s="26"/>
-      <c r="N76" s="8"/>
-      <c r="O76" s="8"/>
-      <c r="Q76" s="2"/>
-    </row>
-    <row r="77" spans="3:17" ht="24.95" customHeight="1">
-      <c r="J77" s="26"/>
-      <c r="K77" s="26"/>
-      <c r="L77" s="26"/>
-      <c r="M77" s="26"/>
-    </row>
-    <row r="78" spans="3:17" ht="24.95" customHeight="1">
-      <c r="J78" s="26"/>
-      <c r="K78" s="26"/>
-      <c r="L78" s="26"/>
-      <c r="M78" s="26"/>
-    </row>
-    <row r="79" spans="3:17" ht="24.95" customHeight="1">
-      <c r="J79" s="26"/>
-      <c r="K79" s="26"/>
-      <c r="L79" s="26"/>
-      <c r="M79" s="26"/>
-    </row>
-    <row r="80" spans="3:17" ht="24.95" customHeight="1">
-      <c r="J80" s="26"/>
-      <c r="K80" s="26"/>
-      <c r="L80" s="26"/>
-      <c r="M80" s="26"/>
+    <row r="70" spans="3:17" ht="24.95" customHeight="1">
+      <c r="J70" s="16"/>
+      <c r="K70" s="16"/>
+      <c r="L70" s="16"/>
+      <c r="M70" s="16"/>
+    </row>
+    <row r="71" spans="3:17" ht="24.95" customHeight="1">
+      <c r="J71" s="16"/>
+      <c r="K71" s="16"/>
+      <c r="L71" s="16"/>
+      <c r="M71" s="16"/>
+    </row>
+    <row r="72" spans="3:17" ht="24.95" customHeight="1">
+      <c r="J72" s="16"/>
+      <c r="K72" s="16"/>
+      <c r="L72" s="16"/>
+      <c r="M72" s="16"/>
+    </row>
+    <row r="73" spans="3:17" ht="24.95" customHeight="1">
+      <c r="J73" s="16"/>
+      <c r="K73" s="16"/>
+      <c r="L73" s="16"/>
+      <c r="M73" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:O22" xr:uid="{E9958AF1-1E2F-4E2C-A9EC-6D24381AE110}"/>
-  <mergeCells count="16">
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="A22:K22"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="K5:K6"/>
+  <autoFilter ref="A6:O16" xr:uid="{E9958AF1-1E2F-4E2C-A9EC-6D24381AE110}"/>
+  <mergeCells count="15">
     <mergeCell ref="A2:O3"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
@@ -3265,6 +2930,10 @@
     <mergeCell ref="I5:I6"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="K5:K6"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.78740157480314965" right="0.59055118110236227" top="0.98425196850393704" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3273,7 +2942,7 @@
     <oddFooter>&amp;LDMS-C-03(Rev.0)&amp;RKorea Infra Management</oddFooter>
   </headerFooter>
   <colBreaks count="1" manualBreakCount="1">
-    <brk id="15" max="16" man="1"/>
+    <brk id="15" max="1048575" man="1"/>
   </colBreaks>
 </worksheet>
 </file>